--- a/downloads/forms/career-cert.xlsx
+++ b/downloads/forms/career-cert.xlsx
@@ -580,7 +580,7 @@
       </c>
     </row>
     <row r="3" ht="17.00787401574803" customHeight="1"/>
-    <row r="4" ht="34.01574803149607" customHeight="1">
+    <row r="4" ht="39.68503937007874" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>인적
@@ -600,7 +600,7 @@
       </c>
       <c r="E4" s="3" t="n"/>
     </row>
-    <row r="5" ht="34.01574803149607" customHeight="1">
+    <row r="5" ht="39.68503937007874" customHeight="1">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
     </row>
-    <row r="6" ht="34.01574803149607" customHeight="1">
+    <row r="6" ht="39.68503937007874" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>경력
@@ -631,7 +631,7 @@
       </c>
       <c r="E6" s="3" t="n"/>
     </row>
-    <row r="7" ht="34.01574803149607" customHeight="1">
+    <row r="7" ht="39.68503937007874" customHeight="1">
       <c r="A7" s="7" t="n"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34.01574803149607" customHeight="1">
+    <row r="8" ht="39.68503937007874" customHeight="1">
       <c r="A8" s="7" t="n"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="6" t="n"/>
     </row>
-    <row r="9" ht="34.01574803149607" customHeight="1">
+    <row r="9" ht="39.68503937007874" customHeight="1">
       <c r="A9" s="7" t="n"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
     </row>
-    <row r="10" ht="34.01574803149607" customHeight="1">
+    <row r="10" ht="39.68503937007874" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="6" t="n"/>
     </row>
-    <row r="11" ht="34.01574803149607" customHeight="1">
+    <row r="11" ht="39.68503937007874" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>회사
@@ -707,7 +707,7 @@
       </c>
       <c r="E11" s="3" t="n"/>
     </row>
-    <row r="12" ht="34.01574803149607" customHeight="1">
+    <row r="12" ht="39.68503937007874" customHeight="1">
       <c r="A12" s="7" t="n"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="E12" s="3" t="n"/>
     </row>
-    <row r="13" ht="34.01574803149607" customHeight="1">
+    <row r="13" ht="39.68503937007874" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
